--- a/diseases/d028/1995-1999.xlsx
+++ b/diseases/d028/1995-1999.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>106</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>15</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>90</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>14</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>27</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>15</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>42</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>5</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>20</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>1</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>34</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5088,9 +5055,6 @@
       <c r="O24" t="n">
         <v>9</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5481,9 +5445,6 @@
       <c r="O26" t="n">
         <v>31</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5874,9 +5835,6 @@
       <c r="O28" t="n">
         <v>5</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6267,9 +6225,6 @@
       <c r="O30" t="n">
         <v>23</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6660,9 +6615,6 @@
       <c r="O32" t="n">
         <v>3</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7053,9 +7005,6 @@
       <c r="O34" t="n">
         <v>22</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7446,9 +7395,6 @@
       <c r="O36" t="n">
         <v>5</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7839,9 +7785,6 @@
       <c r="O38" t="n">
         <v>23</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8232,9 +8175,6 @@
       <c r="O40" t="n">
         <v>9</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8625,9 +8565,6 @@
       <c r="O42" t="n">
         <v>35</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9018,9 +8955,6 @@
       <c r="O44" t="n">
         <v>6</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9411,9 +9345,6 @@
       <c r="O46" t="n">
         <v>52</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9804,9 +9735,6 @@
       <c r="O48" t="n">
         <v>2</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10197,9 +10125,6 @@
       <c r="O50" t="n">
         <v>27</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10590,9 +10515,6 @@
       <c r="O52" t="n">
         <v>2</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="S52" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10983,9 +10905,6 @@
       <c r="O54" t="n">
         <v>24</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="S54" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11376,9 +11295,6 @@
       <c r="O56" t="n">
         <v>3</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="S56" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11769,9 +11685,6 @@
       <c r="O58" t="n">
         <v>33</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12162,9 +12075,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12555,9 +12465,6 @@
       <c r="O62" t="n">
         <v>43</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12948,9 +12855,6 @@
       <c r="O64" t="n">
         <v>5</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="S64" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13341,9 +13245,6 @@
       <c r="O66" t="n">
         <v>48</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="S66" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13734,9 +13635,6 @@
       <c r="O68" t="n">
         <v>8</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14127,9 +14025,6 @@
       <c r="O70" t="n">
         <v>29</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14520,9 +14415,6 @@
       <c r="O72" t="n">
         <v>2</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="S72" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14913,9 +14805,6 @@
       <c r="O74" t="n">
         <v>36</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="S74" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15306,9 +15195,6 @@
       <c r="O76" t="n">
         <v>2</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="S76" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15699,9 +15585,6 @@
       <c r="O78" t="n">
         <v>57</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="S78" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16092,9 +15975,6 @@
       <c r="O80" t="n">
         <v>6</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="S80" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16485,9 +16365,6 @@
       <c r="O82" t="n">
         <v>57</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="S82" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16878,9 +16755,6 @@
       <c r="O84" t="n">
         <v>11</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="S84" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17271,9 +17145,6 @@
       <c r="O86" t="n">
         <v>65</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="S86" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17664,9 +17535,6 @@
       <c r="O88" t="n">
         <v>10</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="S88" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18057,9 +17925,6 @@
       <c r="O90" t="n">
         <v>80</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="S90" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18450,9 +18315,6 @@
       <c r="O92" t="n">
         <v>7</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="S92" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18843,9 +18705,6 @@
       <c r="O94" t="n">
         <v>83</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="S94" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19236,9 +19095,6 @@
       <c r="O96" t="n">
         <v>12</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="S96" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19629,9 +19485,6 @@
       <c r="O98" t="n">
         <v>91</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="S98" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20642,9 +20495,6 @@
       <c r="O103" t="n">
         <v>13</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="S103" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21035,9 +20885,6 @@
       <c r="O105" t="n">
         <v>77</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="S105" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21809,9 +21656,6 @@
       <c r="O109" t="n">
         <v>15</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="S109" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22202,9 +22046,6 @@
       <c r="O111" t="n">
         <v>47</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="S111" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22976,9 +22817,6 @@
       <c r="O115" t="n">
         <v>21</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="S115" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23369,9 +23207,6 @@
       <c r="O117" t="n">
         <v>40</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="S117" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24143,9 +23978,6 @@
       <c r="O121" t="n">
         <v>23</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="S121" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24536,9 +24368,6 @@
       <c r="O123" t="n">
         <v>36</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="S123" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25310,9 +25139,6 @@
       <c r="O127" t="n">
         <v>8</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="S127" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25703,9 +25529,6 @@
       <c r="O129" t="n">
         <v>33</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="S129" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26477,9 +26300,6 @@
       <c r="O133" t="n">
         <v>22</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="S133" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26870,9 +26690,6 @@
       <c r="O135" t="n">
         <v>38</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="S135" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27644,9 +27461,6 @@
       <c r="O139" t="n">
         <v>25</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="S139" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28037,9 +27851,6 @@
       <c r="O141" t="n">
         <v>47</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="S141" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28811,9 +28622,6 @@
       <c r="O145" t="n">
         <v>46</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="S145" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29204,9 +29012,6 @@
       <c r="O147" t="n">
         <v>43</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="S147" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29978,9 +29783,6 @@
       <c r="O151" t="n">
         <v>86</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="S151" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30371,9 +30173,6 @@
       <c r="O153" t="n">
         <v>61</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="S153" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31145,9 +30944,6 @@
       <c r="O157" t="n">
         <v>215</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="S157" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31538,9 +31334,6 @@
       <c r="O159" t="n">
         <v>50</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="S159" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32312,9 +32105,6 @@
       <c r="O163" t="n">
         <v>295</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="S163" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32705,9 +32495,6 @@
       <c r="O165" t="n">
         <v>41</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="S165" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33479,9 +33266,6 @@
       <c r="O169" t="n">
         <v>491</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="S169" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33872,9 +33656,6 @@
       <c r="O171" t="n">
         <v>47</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="S171" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35124,9 +34905,6 @@
       <c r="O177" t="n">
         <v>398</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="S177" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35517,9 +35295,6 @@
       <c r="O179" t="n">
         <v>36</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="S179" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36530,9 +36305,6 @@
       <c r="O184" t="n">
         <v>508</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="S184" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36923,9 +36695,6 @@
       <c r="O186" t="n">
         <v>38</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="S186" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -37936,9 +37705,6 @@
       <c r="O191" t="n">
         <v>309</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="S191" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38329,9 +38095,6 @@
       <c r="O193" t="n">
         <v>37</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="S193" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39342,9 +39105,6 @@
       <c r="O198" t="n">
         <v>210</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="S198" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39735,9 +39495,6 @@
       <c r="O200" t="n">
         <v>38</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="S200" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -40748,9 +40505,6 @@
       <c r="O205" t="n">
         <v>188</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="S205" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -41141,9 +40895,6 @@
       <c r="O207" t="n">
         <v>33</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="S207" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -42154,9 +41905,6 @@
       <c r="O212" t="n">
         <v>155</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="S212" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -42547,9 +42295,6 @@
       <c r="O214" t="n">
         <v>38</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="S214" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -43560,9 +43305,6 @@
       <c r="O219" t="n">
         <v>139</v>
       </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
       <c r="S219" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -43953,9 +43695,6 @@
       <c r="O221" t="n">
         <v>123</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="S221" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -44966,9 +44705,6 @@
       <c r="O226" t="n">
         <v>126</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="S226" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -45359,9 +45095,6 @@
       <c r="O228" t="n">
         <v>93</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="S228" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -46372,9 +46105,6 @@
       <c r="O233" t="n">
         <v>194</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="S233" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -46765,9 +46495,6 @@
       <c r="O235" t="n">
         <v>93</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="S235" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -47778,9 +47505,6 @@
       <c r="O240" t="n">
         <v>183</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="S240" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -48171,9 +47895,6 @@
       <c r="O242" t="n">
         <v>123</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="S242" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -49184,9 +48905,6 @@
       <c r="O247" t="n">
         <v>138</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="S247" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -49577,9 +49295,6 @@
       <c r="O249" t="n">
         <v>125</v>
       </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
       <c r="S249" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -50590,9 +50305,6 @@
       <c r="O254" t="n">
         <v>180</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="S254" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -50983,9 +50695,6 @@
       <c r="O256" t="n">
         <v>85</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="S256" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -52235,9 +51944,6 @@
       <c r="O262" t="n">
         <v>165</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="S262" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -52628,9 +52334,6 @@
       <c r="O264" t="n">
         <v>57</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="S264" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -53641,9 +53344,6 @@
       <c r="O269" t="n">
         <v>136</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="S269" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -54034,9 +53734,6 @@
       <c r="O271" t="n">
         <v>58</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="S271" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -55047,9 +54744,6 @@
       <c r="O276" t="n">
         <v>88</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="S276" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -55440,9 +55134,6 @@
       <c r="O278" t="n">
         <v>51</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="S278" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -56453,9 +56144,6 @@
       <c r="O283" t="n">
         <v>79</v>
       </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
       <c r="S283" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -56846,9 +56534,6 @@
       <c r="O285" t="n">
         <v>66</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="S285" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -57859,9 +57544,6 @@
       <c r="O290" t="n">
         <v>42</v>
       </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
       <c r="S290" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -58252,9 +57934,6 @@
       <c r="O292" t="n">
         <v>34</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="S292" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -59265,9 +58944,6 @@
       <c r="O297" t="n">
         <v>63</v>
       </c>
-      <c r="Q297" t="n">
-        <v>0</v>
-      </c>
       <c r="S297" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -59658,9 +59334,6 @@
       <c r="O299" t="n">
         <v>65</v>
       </c>
-      <c r="Q299" t="n">
-        <v>0</v>
-      </c>
       <c r="S299" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -60671,9 +60344,6 @@
       <c r="O304" t="n">
         <v>59</v>
       </c>
-      <c r="Q304" t="n">
-        <v>0</v>
-      </c>
       <c r="S304" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -61064,9 +60734,6 @@
       <c r="O306" t="n">
         <v>102</v>
       </c>
-      <c r="Q306" t="n">
-        <v>0</v>
-      </c>
       <c r="S306" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -62077,9 +61744,6 @@
       <c r="O311" t="n">
         <v>54</v>
       </c>
-      <c r="Q311" t="n">
-        <v>0</v>
-      </c>
       <c r="S311" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -62470,9 +62134,6 @@
       <c r="O313" t="n">
         <v>106</v>
       </c>
-      <c r="Q313" t="n">
-        <v>0</v>
-      </c>
       <c r="S313" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -63483,9 +63144,6 @@
       <c r="O318" t="n">
         <v>115</v>
       </c>
-      <c r="Q318" t="n">
-        <v>0</v>
-      </c>
       <c r="S318" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -63876,9 +63534,6 @@
       <c r="O320" t="n">
         <v>72</v>
       </c>
-      <c r="Q320" t="n">
-        <v>0</v>
-      </c>
       <c r="S320" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -64889,9 +64544,6 @@
       <c r="O325" t="n">
         <v>124</v>
       </c>
-      <c r="Q325" t="n">
-        <v>0</v>
-      </c>
       <c r="S325" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -65282,9 +64934,6 @@
       <c r="O327" t="n">
         <v>119</v>
       </c>
-      <c r="Q327" t="n">
-        <v>0</v>
-      </c>
       <c r="S327" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -66295,9 +65944,6 @@
       <c r="O332" t="n">
         <v>137</v>
       </c>
-      <c r="Q332" t="n">
-        <v>0</v>
-      </c>
       <c r="S332" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -66688,9 +66334,6 @@
       <c r="O334" t="n">
         <v>99</v>
       </c>
-      <c r="Q334" t="n">
-        <v>0</v>
-      </c>
       <c r="S334" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -67700,9 +67343,6 @@
       </c>
       <c r="O339" t="n">
         <v>173</v>
-      </c>
-      <c r="Q339" t="n">
-        <v>0</v>
       </c>
       <c r="S339" t="inlineStr">
         <is>
